--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484065_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484065_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8273</v>
+        <v>7.1417</v>
       </c>
       <c r="E2" t="n">
-        <v>2.6689</v>
+        <v>2.5725</v>
       </c>
       <c r="F2" t="n">
-        <v>5.1584</v>
+        <v>4.5692</v>
       </c>
       <c r="G2" t="n">
         <v>-2.3382</v>
@@ -610,13 +610,13 @@
         <v>2.9758</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6931</v>
+        <v>1.0075</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6407</v>
+        <v>0.5443</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0524</v>
+        <v>0.4632</v>
       </c>
       <c r="V2" t="n">
         <v>5.6951</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0558</v>
+        <v>6.8576</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0763</v>
+        <v>5.5694</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9796</v>
+        <v>1.2882</v>
       </c>
       <c r="G3" t="n">
         <v>6.1055</v>
@@ -688,13 +688,13 @@
         <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7917999999999999</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.357</v>
+        <v>0.1361</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4348</v>
+        <v>-0.1262</v>
       </c>
       <c r="V3" t="n">
         <v>0.9405</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3239</v>
+        <v>5.3046</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4236</v>
+        <v>4.1798</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9004</v>
+        <v>1.1248</v>
       </c>
       <c r="G4" t="n">
         <v>1.6949</v>
@@ -766,13 +766,13 @@
         <v>2.1822</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9149</v>
+        <v>0.8956</v>
       </c>
       <c r="T4" t="n">
-        <v>1.6382</v>
+        <v>1.3945</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7233000000000001</v>
+        <v>-0.4989</v>
       </c>
       <c r="V4" t="n">
         <v>0.532</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.772</v>
+        <v>3.9668</v>
       </c>
       <c r="E5" t="n">
-        <v>5.2244</v>
+        <v>4.3912</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4524</v>
+        <v>-0.4244</v>
       </c>
       <c r="G5" t="n">
         <v>1.5058</v>
@@ -844,13 +844,13 @@
         <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>2.0083</v>
+        <v>1.2031</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8706</v>
+        <v>1.0374</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1376</v>
+        <v>0.1657</v>
       </c>
       <c r="V5" t="n">
         <v>0.266</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.079</v>
+        <v>0.9433</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6647999999999999</v>
+        <v>1.1182</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4142</v>
+        <v>-0.175</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1505</v>
@@ -922,13 +922,13 @@
         <v>2.3806</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.384</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2209</v>
+        <v>0.2325</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7406</v>
+        <v>0.1515</v>
       </c>
       <c r="V6" t="n">
         <v>-1.4724</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4117</v>
+        <v>-0.7739</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3873</v>
+        <v>-0.6934</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0244</v>
+        <v>-0.0805</v>
       </c>
       <c r="G7" t="n">
         <v>0.2394</v>
@@ -1000,13 +1000,13 @@
         <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0873</v>
+        <v>-0.2749</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4535</v>
+        <v>0.1474</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3662</v>
+        <v>-0.4223</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1352</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. BAJJA SANCHEZ</t>
+          <t>X. ASSALIT GARCÍA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0916</v>
+        <v>-0.9427</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4893</v>
+        <v>-0.72</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.2226</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0706</v>
+        <v>-1.707</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9476</v>
+        <v>-1.7135</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.123</v>
+        <v>0.0065</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0605</v>
+        <v>-0.6399</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0605</v>
+        <v>-0.6399</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1311</v>
+        <v>-1.0672</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.0081</v>
+        <v>-1.0737</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.123</v>
+        <v>0.0065</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7935</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>-1.1903</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1984</v>
+        <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7726</v>
+        <v>-0.0453</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4422</v>
+        <v>-0.0963</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3304</v>
+        <v>0.051</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X. ASSALIT GARCÍA</t>
+          <t>O. BAJJA SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.446</v>
+        <v>-1.2676</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1111</v>
+        <v>-0.6933</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3348</v>
+        <v>-0.5742</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.707</v>
+        <v>-1.0706</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.7135</v>
+        <v>-0.9476</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0065</v>
+        <v>-0.123</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6399</v>
+        <v>0.0605</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6399</v>
+        <v>0.0605</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0672</v>
+        <v>-1.1311</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0737</v>
+        <v>-1.0081</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0065</v>
+        <v>-0.123</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3968</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1903</v>
+        <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7935</v>
+        <v>0.1984</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5486</v>
+        <v>0.5966</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4874</v>
+        <v>0.2381</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0612</v>
+        <v>0.3585</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7775</v>
+        <v>-1.4091</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5694</v>
+        <v>-1.201</v>
       </c>
       <c r="F10" t="n">
         <v>-0.2081</v>
@@ -1234,10 +1234,10 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3854</v>
+        <v>-0.017</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2494</v>
+        <v>0.1191</v>
       </c>
       <c r="U10" t="n">
         <v>-0.136</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.1705</v>
+        <v>-1.5419</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1653</v>
+        <v>0.7378</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3358</v>
+        <v>-2.2797</v>
       </c>
       <c r="G11" t="n">
         <v>-3.4767</v>
@@ -1312,13 +1312,13 @@
         <v>0.5952</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4954</v>
+        <v>0.1332</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1643</v>
+        <v>0.4082</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3311</v>
+        <v>-0.275</v>
       </c>
       <c r="V11" t="n">
         <v>1.2065</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2102</v>
+        <v>-3.0713</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6054</v>
+        <v>-2.7471</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6048</v>
+        <v>-0.3242</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1115</v>
@@ -1390,13 +1390,13 @@
         <v>0.1984</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0906</v>
+        <v>0.0482</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0056</v>
+        <v>-0.1473</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.1955</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2065</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.5218</v>
+        <v>-6.2201</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.7485</v>
+        <v>-4.6432</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7734</v>
+        <v>-1.577</v>
       </c>
       <c r="G13" t="n">
         <v>-7.0726</v>
@@ -1468,13 +1468,13 @@
         <v>0.7935</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8496</v>
+        <v>0.452</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9238</v>
+        <v>0.1815</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0742</v>
+        <v>0.2706</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1947</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.428699999999998</v>
+        <v>8.987399999999996</v>
       </c>
       <c r="E14" t="n">
-        <v>6.3123</v>
+        <v>7.870900000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1166</v>
+        <v>1.116500000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-10.1704</v>
@@ -1546,13 +1546,13 @@
         <v>14.8789</v>
       </c>
       <c r="S14" t="n">
-        <v>2.834500000000001</v>
+        <v>4.392900000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6368</v>
+        <v>4.195500000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1975999999999999</v>
+        <v>0.1975999999999998</v>
       </c>
       <c r="V14" t="n">
         <v>5.837800000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2107</v>
+        <v>2.0866</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6893</v>
+        <v>1.0771</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5214</v>
+        <v>1.0095</v>
       </c>
       <c r="G15" t="n">
         <v>0.6619</v>
@@ -1624,13 +1624,13 @@
         <v>0.9919</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0169</v>
+        <v>0.8927</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7427</v>
+        <v>0.1305</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2742</v>
+        <v>0.7622</v>
       </c>
       <c r="V15" t="n">
         <v>0.532</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4317</v>
+        <v>1.5158</v>
       </c>
       <c r="E16" t="n">
         <v>1.2431</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1885</v>
+        <v>0.2727</v>
       </c>
       <c r="G16" t="n">
         <v>1.4464</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.352</v>
+        <v>-0.2678</v>
       </c>
       <c r="T16" t="n">
         <v>-0.0623</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2897</v>
+        <v>-0.2055</v>
       </c>
       <c r="V16" t="n">
         <v>0.3373</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1959</v>
+        <v>0.6934</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.244</v>
+        <v>-0.5501</v>
       </c>
       <c r="F17" t="n">
-        <v>1.44</v>
+        <v>1.2436</v>
       </c>
       <c r="G17" t="n">
         <v>-0.7359</v>
@@ -1780,13 +1780,13 @@
         <v>0.1984</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1185</v>
+        <v>-0.384</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4422</v>
+        <v>0.1361</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3237</v>
+        <v>-0.5201</v>
       </c>
       <c r="V17" t="n">
         <v>1.615</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9003</v>
+        <v>0.3264</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9832</v>
+        <v>0.269</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0829</v>
+        <v>0.0574</v>
       </c>
       <c r="G18" t="n">
         <v>1.01</v>
@@ -1858,13 +1858,13 @@
         <v>0.5952</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5016</v>
+        <v>-0.0723</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6122</v>
+        <v>-0.102</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1106</v>
+        <v>0.0297</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2065</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. NEBRA SANCHEZ</t>
+          <t>M. SMITH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2034</v>
+        <v>0.107</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4661</v>
+        <v>0.241</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6695</v>
+        <v>-0.134</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0005</v>
+        <v>-0.7462</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2802</v>
+        <v>0.6142</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7204</v>
+        <v>-1.3604</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6531</v>
+        <v>0.064</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6129</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0402</v>
+        <v>-0.7127</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3474</v>
+        <v>-0.8102</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3328</v>
+        <v>-0.1625</v>
       </c>
       <c r="O19" t="n">
-        <v>0.6802</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5952</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1202</v>
+        <v>0.1743</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.187</v>
+        <v>0.0852</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0668</v>
+        <v>0.0891</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.6789</v>
+        <v>1.4724</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.0757</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.6789</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. CORTES ALEJANDRE</t>
+          <t>J. NEBRA SANCHEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8462</v>
+        <v>-0.2136</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2064</v>
+        <v>1.5681</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3602</v>
+        <v>-1.7817</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.31</v>
+        <v>2.0005</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1462</v>
+        <v>1.2802</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.4563</v>
+        <v>0.7204</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.3903</v>
+        <v>1.6531</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6101</v>
+        <v>1.6129</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.0004</v>
+        <v>0.0402</v>
       </c>
       <c r="M20" t="n">
-        <v>0.08019999999999999</v>
+        <v>0.3474</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4639</v>
+        <v>-0.3328</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5442</v>
+        <v>0.6802</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1394</v>
+        <v>-0.1304</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2551</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3945</v>
+        <v>-0.0454</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6032</v>
+        <v>-2.6789</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.0713</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.6745</v>
+        <v>-2.6789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. BOUSALEM GARZA</t>
+          <t>D. CORTES ALEJANDRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,40 +2047,40 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3374</v>
+        <v>-0.8258</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0561</v>
+        <v>-1.4105</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2812</v>
+        <v>0.5847</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.333</v>
+        <v>-1.31</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4213</v>
+        <v>0.1462</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0883</v>
+        <v>-1.4563</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6197</v>
+        <v>-1.3903</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6197</v>
+        <v>0.6101</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-2.0004</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2867</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8016</v>
+        <v>-0.4639</v>
       </c>
       <c r="O21" t="n">
-        <v>1.0883</v>
+        <v>0.5442</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
@@ -2092,28 +2092,28 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0044</v>
+        <v>-0.119</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4364</v>
+        <v>0.0511</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.1701</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.0713</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SMITH</t>
+          <t>I. BOUSALEM GARZA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5314</v>
+        <v>-0.897</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8813</v>
+        <v>-1.0561</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6501</v>
+        <v>0.1592</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7462</v>
+        <v>-0.333</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6142</v>
+        <v>-1.4213</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3604</v>
+        <v>1.0883</v>
       </c>
       <c r="J22" t="n">
-        <v>0.064</v>
+        <v>-0.6197</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7766999999999999</v>
+        <v>-0.6197</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7127</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8102</v>
+        <v>0.2867</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1625</v>
+        <v>-0.8016</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6477000000000001</v>
+        <v>1.0883</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7935</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1903</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4641</v>
+        <v>-0.5639999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0372</v>
+        <v>-0.4364</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.427</v>
+        <v>-0.1276</v>
       </c>
       <c r="V22" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.0757</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6032</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. PAÑART POSTIGO</t>
+          <t>A. VICENTE ALONSO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9946</v>
+        <v>-1.3585</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.738</v>
+        <v>0.7023</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.2566</v>
+        <v>-2.0608</v>
       </c>
       <c r="G23" t="n">
-        <v>1.5366</v>
+        <v>2.3665</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5924</v>
+        <v>2.3277</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.0557</v>
+        <v>0.0388</v>
       </c>
       <c r="J23" t="n">
-        <v>1.5632</v>
+        <v>3.1914</v>
       </c>
       <c r="K23" t="n">
-        <v>1.6384</v>
+        <v>2.0968</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0752</v>
+        <v>1.0946</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0265</v>
+        <v>-0.8249</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.046</v>
+        <v>0.2309</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0195</v>
+        <v>-1.0558</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3887</v>
+        <v>-2.3806</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9838</v>
+        <v>-2.9758</v>
       </c>
       <c r="R23" t="n">
         <v>0.5952</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4041</v>
+        <v>-0.4039</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3173</v>
+        <v>-0.0452</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0868</v>
+        <v>-0.3586</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7384</v>
+        <v>-0.9405</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.7384</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. NUÑEZ NAVARRO</t>
+          <t>B. PAÑART POSTIGO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1892</v>
+        <v>-1.47</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2173</v>
+        <v>-0.738</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.9719</v>
+        <v>-0.732</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9779</v>
+        <v>1.5366</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6099</v>
+        <v>1.5924</v>
       </c>
       <c r="I24" t="n">
-        <v>0.368</v>
+        <v>-0.0557</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3584</v>
+        <v>1.5632</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5953000000000001</v>
+        <v>1.6384</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7631</v>
+        <v>-0.0752</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3805</v>
+        <v>-0.0265</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0147</v>
+        <v>-0.046</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.3951</v>
+        <v>0.0195</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6116</v>
+        <v>0.1205</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2267</v>
+        <v>-0.3173</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3849</v>
+        <v>0.4378</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.5555</v>
+        <v>-1.7384</v>
       </c>
       <c r="W24" t="n">
-        <v>-1.349</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2065</v>
+        <v>-1.7384</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A. VICENTE ALONSO</t>
+          <t>A. NUÑEZ NAVARRO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.4187</v>
+        <v>-1.6952</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1139</v>
+        <v>0.0887</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3048</v>
+        <v>-1.7839</v>
       </c>
       <c r="G25" t="n">
-        <v>2.3665</v>
+        <v>0.9779</v>
       </c>
       <c r="H25" t="n">
-        <v>2.3277</v>
+        <v>0.6099</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0388</v>
+        <v>0.368</v>
       </c>
       <c r="J25" t="n">
-        <v>3.1914</v>
+        <v>1.3584</v>
       </c>
       <c r="K25" t="n">
-        <v>2.0968</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>1.0946</v>
+        <v>0.7631</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8249</v>
+        <v>-0.3805</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2309</v>
+        <v>0.0147</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0558</v>
+        <v>-0.3951</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.3806</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4641</v>
+        <v>-0.1176</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8615</v>
+        <v>0.0794</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6027</v>
+        <v>-0.197</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.9405</v>
+        <v>-2.5555</v>
       </c>
       <c r="W25" t="n">
-        <v>0.532</v>
+        <v>-1.349</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.6464</v>
+        <v>-2.9771</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.0411</v>
+        <v>-2.5512</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6052999999999999</v>
+        <v>-0.4259</v>
       </c>
       <c r="G26" t="n">
         <v>3.2957</v>
@@ -2482,13 +2482,13 @@
         <v>1.1903</v>
       </c>
       <c r="S26" t="n">
-        <v>1.0888</v>
+        <v>0.7581</v>
       </c>
       <c r="T26" t="n">
-        <v>0.8787</v>
+        <v>0.3686</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2101</v>
+        <v>0.3895</v>
       </c>
       <c r="V26" t="n">
         <v>-1.2777</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.428699999999999</v>
+        <v>-4.708</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.1164</v>
+        <v>-1.1166</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.312199999999999</v>
+        <v>-3.5912</v>
       </c>
       <c r="G27" t="n">
         <v>10.1704</v>
@@ -2560,13 +2560,13 @@
         <v>5.9517</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.834099999999999</v>
+        <v>-0.1133999999999998</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.1975</v>
+        <v>-0.1973000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-2.6368</v>
+        <v>0.08400000000000002</v>
       </c>
       <c r="V27" t="n">
         <v>-5.8376</v>
